--- a/stats_sheet.xlsx
+++ b/stats_sheet.xlsx
@@ -8,12 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Omri\Desktop\omri\לימודים והוראה\תואר ראשון\סמסטר 7\פרויקט גמר\git_repo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90CD7188-2AA0-40EF-AB82-D15E1A21C791}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C598F0F-E53F-4181-A70E-14B303680CC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="SARSA_lambda - single iteration" sheetId="4" r:id="rId1"/>
+    <sheet name="SARSA_lambda - batch collected" sheetId="3" r:id="rId2"/>
+    <sheet name="archive2 - dont use" sheetId="1" r:id="rId3"/>
+    <sheet name="archive1 - dont use" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,12 +36,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="6">
   <si>
     <t>iteration/time step</t>
   </si>
   <si>
     <t>Average</t>
+  </si>
+  <si>
+    <t>iteration/time step [SARSA]</t>
+  </si>
+  <si>
+    <t>Average [SARSA]</t>
+  </si>
+  <si>
+    <t>Average [SARSA_lambda]</t>
+  </si>
+  <si>
+    <t>iteration/time step [SARSA_lambda]</t>
   </si>
 </sst>
 </file>
@@ -156,7 +171,7 @@
             </a:r>
             <a:r>
               <a:rPr lang="en-US" baseline="0"/>
-              <a:t> direction - performence in each iteration (colors are time steps)</a:t>
+              <a:t> direction - performence in each iteration (colors are time steps) [SARSA_lambda]</a:t>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -202,11 +217,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$B$1</c:f>
+              <c:f>'SARSA_lambda - single iteration'!$B$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>1000</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -237,7 +252,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$6</c:f>
+              <c:f>'SARSA_lambda - single iteration'!$A$2:$A$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -261,32 +276,17 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$B$2:$B$6</c:f>
+              <c:f>'SARSA_lambda - single iteration'!$B$2:$B$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>0.14984391259105109</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.536885245901643E-2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>6.2500000000000524E-3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.41748768472906422</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.27104959630911191</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-61D2-4E0E-AEF2-8993E218E1FF}"/>
+              <c16:uniqueId val="{00000000-A074-4A0E-A749-4A731B14CE72}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -295,11 +295,11 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$C$1</c:f>
+              <c:f>'SARSA_lambda - single iteration'!$C$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>10000</c:v>
+                  <c:v>20000</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -330,7 +330,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$6</c:f>
+              <c:f>'SARSA_lambda - single iteration'!$A$2:$A$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -354,32 +354,17 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$C$2:$C$6</c:f>
+              <c:f>'SARSA_lambda - single iteration'!$C$2:$C$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>0.14984391259105109</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.434426229508203E-2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>6.2500000000000524E-3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.3041871921182267</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.22260668973471739</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-61D2-4E0E-AEF2-8993E218E1FF}"/>
+              <c16:uniqueId val="{00000001-A074-4A0E-A749-4A731B14CE72}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -388,11 +373,11 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$D$1</c:f>
+              <c:f>'SARSA_lambda - single iteration'!$D$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>100000</c:v>
+                  <c:v>40000</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -423,7 +408,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$6</c:f>
+              <c:f>'SARSA_lambda - single iteration'!$A$2:$A$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -447,32 +432,17 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$D$2:$D$6</c:f>
+              <c:f>'SARSA_lambda - single iteration'!$D$2:$D$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>0.24037460978147759</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.24795081967213109</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.13958333333333331</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.4261083743842366</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.23760092272203001</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-61D2-4E0E-AEF2-8993E218E1FF}"/>
+              <c16:uniqueId val="{00000002-A074-4A0E-A749-4A731B14CE72}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -481,11 +451,11 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$E$1</c:f>
+              <c:f>'SARSA_lambda - single iteration'!$E$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>1000000</c:v>
+                  <c:v>60000</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -516,7 +486,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$6</c:f>
+              <c:f>'SARSA_lambda - single iteration'!$A$2:$A$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -540,32 +510,17 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$E$2:$E$6</c:f>
+              <c:f>'SARSA_lambda - single iteration'!$E$2:$E$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>9.8855359001040519E-2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.30635245901639352</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.16770833333333329</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.31403940886699522</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.110726643598616</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-A38E-49F7-BA1C-91C7FFD505F2}"/>
+              <c16:uniqueId val="{00000003-A074-4A0E-A749-4A731B14CE72}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -574,11 +529,11 @@
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$F$1</c:f>
+              <c:f>'SARSA_lambda - single iteration'!$F$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>10000000</c:v>
+                  <c:v>80000</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -609,7 +564,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$A$2:$A$6</c:f>
+              <c:f>'SARSA_lambda - single iteration'!$A$2:$A$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -633,32 +588,95 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$F$2:$F$6</c:f>
+              <c:f>'SARSA_lambda - single iteration'!$F$2:$F$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>0.20811654526534859</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.12909836065573771</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.2479166666666667</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.2450738916256158</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.25836216839677051</c:v>
-                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-A38E-49F7-BA1C-91C7FFD505F2}"/>
+              <c16:uniqueId val="{00000004-A074-4A0E-A749-4A731B14CE72}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'SARSA_lambda - single iteration'!$G$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>100000</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent6"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'SARSA_lambda - single iteration'!$A$2:$A$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'SARSA_lambda - single iteration'!$G$2:$G$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-A074-4A0E-A749-4A731B14CE72}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -960,11 +978,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$25</c:f>
+              <c:f>'SARSA_lambda - single iteration'!$A$25</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Average</c:v>
+                  <c:v>Average [SARSA_lambda]</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -995,7 +1013,2348 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Sheet1!$B$24:$G$24</c:f>
+              <c:f>'SARSA_lambda - single iteration'!$B$24:$G$24</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>40000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>60000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>80000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>100000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'SARSA_lambda - single iteration'!$B$25:$G$25</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-8B1B-414E-8383-0B556F3D9FAD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="904230895"/>
+        <c:axId val="904222735"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="904230895"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="he-IL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="904222735"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="904222735"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="he-IL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="904230895"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="he-IL"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Vertical</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> direction - performence in each iteration (colors are time steps) [SARSA_lambda]</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="he-IL"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'SARSA_lambda - batch collected'!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>10000</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'SARSA_lambda - batch collected'!$A$2:$A$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'SARSA_lambda - batch collected'!$B$2:$B$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.20361560418648911</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.16950596252129471</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.2214428857715432</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-0.46385542168674693</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.20296570898980529</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0FB7-42C6-A89A-C26E2A72C8F1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'SARSA_lambda - batch collected'!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>20000</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'SARSA_lambda - batch collected'!$A$2:$A$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'SARSA_lambda - batch collected'!$C$2:$C$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2.0932445290199869E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.1984667802385009</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.22344689378757521</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-0.27831325301204801</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.18535681186283601</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-0FB7-42C6-A89A-C26E2A72C8F1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'SARSA_lambda - batch collected'!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>40000</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'SARSA_lambda - batch collected'!$A$2:$A$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'SARSA_lambda - batch collected'!$D$2:$D$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>5.5185537583254049E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7.06984667802385E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-8.8176352705410715E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-0.25421686746987943</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.2632066728452191E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-0FB7-42C6-A89A-C26E2A72C8F1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'SARSA_lambda - batch collected'!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>60000</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'SARSA_lambda - batch collected'!$A$2:$A$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'SARSA_lambda - batch collected'!$E$2:$E$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>7.9923882017126538E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7.8364565587734233E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-8.5170340681362686E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-0.39879518072289138</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-1.668211306765538E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-0FB7-42C6-A89A-C26E2A72C8F1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'SARSA_lambda - batch collected'!$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>80000</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent5"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'SARSA_lambda - batch collected'!$A$2:$A$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'SARSA_lambda - batch collected'!$F$2:$F$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.2216936251189344</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7.7512776831345831E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-9.8196392785571185E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-0.23012048192771081</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.7071362372567057E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-0FB7-42C6-A89A-C26E2A72C8F1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'SARSA_lambda - batch collected'!$G$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>100000</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent6"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'SARSA_lambda - batch collected'!$A$2:$A$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'SARSA_lambda - batch collected'!$G$2:$G$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.2131303520456708</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.16609880749574121</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-8.717434869739471E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-0.21325301204819269</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-0.1075069508804449</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-0FB7-42C6-A89A-C26E2A72C8F1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1001866000"/>
+        <c:axId val="1001868880"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1001866000"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="he-IL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1001868880"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1001868880"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="he-IL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1001866000"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="he-IL"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="he-IL"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Average(time steps)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="he-IL"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'SARSA_lambda - batch collected'!$A$25</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Average [SARSA_lambda]</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'SARSA_lambda - batch collected'!$B$24:$G$24</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>40000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>60000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>80000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>100000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'SARSA_lambda - batch collected'!$B$25:$G$25</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>6.6734947956477081E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6.9977935633412786E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-3.4775429816669076E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-6.8471837373409741E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.5921779219130628E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-5.7410304169240589E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-B219-401B-B90A-56FBA219BECA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="904230895"/>
+        <c:axId val="904222735"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="904230895"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="he-IL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="904222735"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="904222735"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="he-IL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="904230895"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="he-IL"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Vertical</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> direction - performence in each iteration (colors are time steps) [SARSA]</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="he-IL"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'archive2 - dont use'!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1000</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'archive2 - dont use'!$A$2:$A$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'archive2 - dont use'!$B$2:$B$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>-0.31316725978647703</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-9.6866096866096998E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-1.098901098901095E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-4.5602605863192168E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.14990859232175491</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-61D2-4E0E-AEF2-8993E218E1FF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'archive2 - dont use'!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>10000</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'archive2 - dont use'!$A$2:$A$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'archive2 - dont use'!$C$2:$C$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>-0.19572953736654811</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6.2678062678062696E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-0.22857142857142859</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-0.1368078175895765</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.828153564899445E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-61D2-4E0E-AEF2-8993E218E1FF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'archive2 - dont use'!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>100000</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'archive2 - dont use'!$A$2:$A$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'archive2 - dont use'!$D$2:$D$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>-0.30367734282325037</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.11680911680911669</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-0.26923076923076938</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-0.11617806731813229</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.31809872029250452</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-61D2-4E0E-AEF2-8993E218E1FF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'archive2 - dont use'!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1000000</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'archive2 - dont use'!$A$2:$A$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'archive2 - dont use'!$E$2:$E$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>-0.21826809015421109</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.5584045584045461E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-0.1373626373626374</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-8.3604777415852274E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.279707495429605E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-A38E-49F7-BA1C-91C7FFD505F2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'archive2 - dont use'!$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>10000000</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent5"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'archive2 - dont use'!$A$2:$A$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'archive2 - dont use'!$F$2:$F$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>-0.23368920521945441</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-1.2345679012345749E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-8.3516483516483497E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-0.13897937024972851</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.1188299817184643</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-A38E-49F7-BA1C-91C7FFD505F2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1001866000"/>
+        <c:axId val="1001868880"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1001866000"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="he-IL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1001868880"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1001868880"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="he-IL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1001866000"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="he-IL"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="he-IL"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Average(time steps)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="he-IL"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'archive2 - dont use'!$A$25</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Average [SARSA]</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'archive2 - dont use'!$B$24:$G$24</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -1022,27 +3381,27 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Sheet1!$B$25:$G$25</c:f>
+              <c:f>'archive2 - dont use'!$B$25:$G$25</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0.17533869343329442</c:v>
+                  <c:v>-6.3343276236604434E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.12342384583238049</c:v>
+                  <c:v>-9.6029837040099209E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.19173486989629204</c:v>
+                  <c:v>-5.0835668454106163E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.19686953049049599</c:v>
+                  <c:v>-7.6170876878871849E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.15502010843522235</c:v>
+                  <c:v>-6.9940151255909563E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.15190640647955672</c:v>
+                  <c:v>-3.4748687940742908E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1051,6 +3410,1130 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-5830-4C51-B509-BA06E51EB2A1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="904230895"/>
+        <c:axId val="904222735"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="904230895"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="he-IL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="904222735"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="904222735"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="he-IL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="904230895"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="he-IL"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Vertical</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> direction - performence in each iteration (colors are time steps)</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="he-IL"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'archive1 - dont use'!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1000</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'archive1 - dont use'!$A$2:$A$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'archive1 - dont use'!$B$2:$B$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.14984391259105109</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.536885245901643E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6.2500000000000524E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.41748768472906422</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.27104959630911191</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0E63-4AEF-8848-F64725E20160}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'archive1 - dont use'!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>10000</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'archive1 - dont use'!$A$2:$A$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'archive1 - dont use'!$C$2:$C$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.14984391259105109</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.434426229508203E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6.2500000000000524E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.3041871921182267</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.22260668973471739</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-0E63-4AEF-8848-F64725E20160}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'archive1 - dont use'!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>100000</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'archive1 - dont use'!$A$2:$A$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'archive1 - dont use'!$D$2:$D$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.24037460978147759</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.24795081967213109</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.13958333333333331</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.4261083743842366</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.23760092272203001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-0E63-4AEF-8848-F64725E20160}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'archive1 - dont use'!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>1000000</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'archive1 - dont use'!$A$2:$A$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'archive1 - dont use'!$E$2:$E$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>9.8855359001040519E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.30635245901639352</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.16770833333333329</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.31403940886699522</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.110726643598616</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-0E63-4AEF-8848-F64725E20160}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'archive1 - dont use'!$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>10000000</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent5"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'archive1 - dont use'!$A$2:$A$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'archive1 - dont use'!$F$2:$F$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.20811654526534859</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.12909836065573771</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.2479166666666667</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.2450738916256158</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.25836216839677051</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-0E63-4AEF-8848-F64725E20160}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1001866000"/>
+        <c:axId val="1001868880"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1001866000"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="he-IL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1001868880"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1001868880"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="he-IL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1001866000"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="he-IL"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="he-IL"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Average(time steps)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="he-IL"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'archive1 - dont use'!$A$25</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Average</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'archive1 - dont use'!$B$24:$G$24</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>100000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1000000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10000000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>100000000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'archive1 - dont use'!$B$25:$G$25</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0.17533869343329442</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.12342384583238049</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.19173486989629204</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.19686953049049599</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.15502010843522235</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.15190640647955672</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-EA6A-4BFF-AF9A-E513CCFD28B4}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1321,6 +4804,246 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -2353,7 +6076,3342 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>276225</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>38099</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB0C2D43-0B02-4BE4-B044-BAB44EE458F5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>590549</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{14A3F5B5-9D4C-44B5-92B1-934C6507AFB0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>276225</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>38099</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AF38A874-1C49-49DC-A313-2E16DCF295A0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>590549</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E0A63E57-9880-49F7-A223-F23751C9E409}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>276225</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>38099</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10E2F16F-ECE1-CF85-2D35-FC7CDF2BD8EA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>590549</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3CB6FE3D-F70B-FB37-EC2B-F80CC2A0445C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -2370,14 +9428,16 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Chart 3">
+        <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10E2F16F-ECE1-CF85-2D35-FC7CDF2BD8EA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D44C731-92C3-414F-9D34-D8E02D1DB879}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -2406,14 +9466,16 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="6" name="Chart 5">
+        <xdr:cNvPr id="3" name="Chart 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3CB6FE3D-F70B-FB37-EC2B-F80CC2A0445C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{051CEB32-7047-4E65-B2B2-043E977FF6CE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -2714,7 +9776,715 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BC9AB2A-6352-4196-8ED0-5223EC79D880}">
+  <dimension ref="A1:G25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="30.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="1">
+        <v>10000</v>
+      </c>
+      <c r="C1" s="1">
+        <v>20000</v>
+      </c>
+      <c r="D1" s="1">
+        <v>40000</v>
+      </c>
+      <c r="E1" s="1">
+        <v>60000</v>
+      </c>
+      <c r="F1" s="1">
+        <v>80000</v>
+      </c>
+      <c r="G1" s="1">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="2" t="e">
+        <f t="shared" ref="B12:G12" si="0">AVERAGE(B2:B11)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="C12" s="2" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D12" s="2" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E12" s="2" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F12" s="2" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G12" s="2" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A24" s="2" t="str">
+        <f t="shared" ref="A24:G24" si="1">A1</f>
+        <v>iteration/time step [SARSA_lambda]</v>
+      </c>
+      <c r="B24" s="2">
+        <f t="shared" si="1"/>
+        <v>10000</v>
+      </c>
+      <c r="C24" s="2">
+        <f t="shared" si="1"/>
+        <v>20000</v>
+      </c>
+      <c r="D24" s="2">
+        <f t="shared" si="1"/>
+        <v>40000</v>
+      </c>
+      <c r="E24" s="2">
+        <f t="shared" si="1"/>
+        <v>60000</v>
+      </c>
+      <c r="F24" s="2">
+        <f t="shared" si="1"/>
+        <v>80000</v>
+      </c>
+      <c r="G24" s="2">
+        <f t="shared" si="1"/>
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A25" s="2" t="str">
+        <f t="shared" ref="A25:G25" si="2">A12</f>
+        <v>Average [SARSA_lambda]</v>
+      </c>
+      <c r="B25" s="2" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="C25" s="2" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D25" s="2" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E25" s="2" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F25" s="2" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G25" s="2" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF86AA52-36E6-4D58-90CB-5B8463848E7A}">
+  <dimension ref="A1:G25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="30.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="1">
+        <v>10000</v>
+      </c>
+      <c r="C1" s="1">
+        <v>20000</v>
+      </c>
+      <c r="D1" s="1">
+        <v>40000</v>
+      </c>
+      <c r="E1" s="1">
+        <v>60000</v>
+      </c>
+      <c r="F1" s="1">
+        <v>80000</v>
+      </c>
+      <c r="G1" s="1">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.20361560418648911</v>
+      </c>
+      <c r="C2">
+        <v>2.0932445290199869E-2</v>
+      </c>
+      <c r="D2">
+        <v>5.5185537583254049E-2</v>
+      </c>
+      <c r="E2">
+        <v>7.9923882017126538E-2</v>
+      </c>
+      <c r="F2">
+        <v>0.2216936251189344</v>
+      </c>
+      <c r="G2">
+        <v>0.2131303520456708</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>0.16950596252129471</v>
+      </c>
+      <c r="C3">
+        <v>0.1984667802385009</v>
+      </c>
+      <c r="D3">
+        <v>7.06984667802385E-2</v>
+      </c>
+      <c r="E3">
+        <v>7.8364565587734233E-2</v>
+      </c>
+      <c r="F3">
+        <v>7.7512776831345831E-2</v>
+      </c>
+      <c r="G3">
+        <v>0.16609880749574121</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>0.2214428857715432</v>
+      </c>
+      <c r="C4">
+        <v>0.22344689378757521</v>
+      </c>
+      <c r="D4">
+        <v>-8.8176352705410715E-2</v>
+      </c>
+      <c r="E4">
+        <v>-8.5170340681362686E-2</v>
+      </c>
+      <c r="F4">
+        <v>-9.8196392785571185E-2</v>
+      </c>
+      <c r="G4">
+        <v>-8.717434869739471E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>-0.46385542168674693</v>
+      </c>
+      <c r="C5">
+        <v>-0.27831325301204801</v>
+      </c>
+      <c r="D5">
+        <v>-0.25421686746987943</v>
+      </c>
+      <c r="E5">
+        <v>-0.39879518072289138</v>
+      </c>
+      <c r="F5">
+        <v>-0.23012048192771081</v>
+      </c>
+      <c r="G5">
+        <v>-0.21325301204819269</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>0.20296570898980529</v>
+      </c>
+      <c r="C6">
+        <v>0.18535681186283601</v>
+      </c>
+      <c r="D6">
+        <v>4.2632066728452191E-2</v>
+      </c>
+      <c r="E6">
+        <v>-1.668211306765538E-2</v>
+      </c>
+      <c r="F6">
+        <v>3.7071362372567057E-2</v>
+      </c>
+      <c r="G6">
+        <v>-0.1075069508804449</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="2">
+        <f t="shared" ref="B12:G12" si="0">AVERAGE(B2:B11)</f>
+        <v>6.6734947956477081E-2</v>
+      </c>
+      <c r="C12" s="2">
+        <f t="shared" si="0"/>
+        <v>6.9977935633412786E-2</v>
+      </c>
+      <c r="D12" s="2">
+        <f t="shared" si="0"/>
+        <v>-3.4775429816669076E-2</v>
+      </c>
+      <c r="E12" s="2">
+        <f t="shared" si="0"/>
+        <v>-6.8471837373409741E-2</v>
+      </c>
+      <c r="F12" s="2">
+        <f t="shared" si="0"/>
+        <v>1.5921779219130628E-3</v>
+      </c>
+      <c r="G12" s="2">
+        <f t="shared" si="0"/>
+        <v>-5.7410304169240589E-3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A24" s="2" t="str">
+        <f t="shared" ref="A24:G24" si="1">A1</f>
+        <v>iteration/time step [SARSA_lambda]</v>
+      </c>
+      <c r="B24" s="2">
+        <f t="shared" si="1"/>
+        <v>10000</v>
+      </c>
+      <c r="C24" s="2">
+        <f t="shared" si="1"/>
+        <v>20000</v>
+      </c>
+      <c r="D24" s="2">
+        <f t="shared" si="1"/>
+        <v>40000</v>
+      </c>
+      <c r="E24" s="2">
+        <f t="shared" si="1"/>
+        <v>60000</v>
+      </c>
+      <c r="F24" s="2">
+        <f t="shared" si="1"/>
+        <v>80000</v>
+      </c>
+      <c r="G24" s="2">
+        <f t="shared" si="1"/>
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A25" s="2" t="str">
+        <f t="shared" ref="A25:G25" si="2">A12</f>
+        <v>Average [SARSA_lambda]</v>
+      </c>
+      <c r="B25" s="2">
+        <f t="shared" si="2"/>
+        <v>6.6734947956477081E-2</v>
+      </c>
+      <c r="C25" s="2">
+        <f t="shared" si="2"/>
+        <v>6.9977935633412786E-2</v>
+      </c>
+      <c r="D25" s="2">
+        <f t="shared" si="2"/>
+        <v>-3.4775429816669076E-2</v>
+      </c>
+      <c r="E25" s="2">
+        <f t="shared" si="2"/>
+        <v>-6.8471837373409741E-2</v>
+      </c>
+      <c r="F25" s="2">
+        <f t="shared" si="2"/>
+        <v>1.5921779219130628E-3</v>
+      </c>
+      <c r="G25" s="2">
+        <f t="shared" si="2"/>
+        <v>-5.7410304169240589E-3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="23.25" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C1" s="1">
+        <v>10000</v>
+      </c>
+      <c r="D1" s="1">
+        <v>100000</v>
+      </c>
+      <c r="E1" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="F1" s="1">
+        <v>10000000</v>
+      </c>
+      <c r="G1" s="1">
+        <v>100000000</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>-0.31316725978647703</v>
+      </c>
+      <c r="C2">
+        <v>-0.19572953736654811</v>
+      </c>
+      <c r="D2">
+        <v>-0.30367734282325037</v>
+      </c>
+      <c r="E2">
+        <v>-0.21826809015421109</v>
+      </c>
+      <c r="F2">
+        <v>-0.23368920521945441</v>
+      </c>
+      <c r="G2">
+        <v>-3.4400948991696427E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>-9.6866096866096998E-2</v>
+      </c>
+      <c r="C3">
+        <v>6.2678062678062696E-2</v>
+      </c>
+      <c r="D3">
+        <v>0.11680911680911669</v>
+      </c>
+      <c r="E3">
+        <v>4.5584045584045461E-2</v>
+      </c>
+      <c r="F3">
+        <v>-1.2345679012345749E-2</v>
+      </c>
+      <c r="G3">
+        <v>-6.7426400759734176E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>-1.098901098901095E-2</v>
+      </c>
+      <c r="C4">
+        <v>-0.22857142857142859</v>
+      </c>
+      <c r="D4">
+        <v>-0.26923076923076938</v>
+      </c>
+      <c r="E4">
+        <v>-0.1373626373626374</v>
+      </c>
+      <c r="F4">
+        <v>-8.3516483516483497E-2</v>
+      </c>
+      <c r="G4">
+        <v>-0.19010989010989021</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>-4.5602605863192168E-2</v>
+      </c>
+      <c r="C5">
+        <v>-0.1368078175895765</v>
+      </c>
+      <c r="D5">
+        <v>-0.11617806731813229</v>
+      </c>
+      <c r="E5">
+        <v>-8.3604777415852274E-2</v>
+      </c>
+      <c r="F5">
+        <v>-0.13897937024972851</v>
+      </c>
+      <c r="G5">
+        <v>-2.714440825190011E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>0.14990859232175491</v>
+      </c>
+      <c r="C6">
+        <v>1.828153564899445E-2</v>
+      </c>
+      <c r="D6">
+        <v>0.31809872029250452</v>
+      </c>
+      <c r="E6">
+        <v>1.279707495429605E-2</v>
+      </c>
+      <c r="F6">
+        <v>0.1188299817184643</v>
+      </c>
+      <c r="G6">
+        <v>0.1453382084095064</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="2">
+        <f t="shared" ref="B12:G12" si="0">AVERAGE(B2:B11)</f>
+        <v>-6.3343276236604434E-2</v>
+      </c>
+      <c r="C12" s="2">
+        <f t="shared" si="0"/>
+        <v>-9.6029837040099209E-2</v>
+      </c>
+      <c r="D12" s="2">
+        <f t="shared" si="0"/>
+        <v>-5.0835668454106163E-2</v>
+      </c>
+      <c r="E12" s="2">
+        <f t="shared" si="0"/>
+        <v>-7.6170876878871849E-2</v>
+      </c>
+      <c r="F12" s="2">
+        <f t="shared" si="0"/>
+        <v>-6.9940151255909563E-2</v>
+      </c>
+      <c r="G12" s="2">
+        <f t="shared" si="0"/>
+        <v>-3.4748687940742908E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A24" s="2" t="str">
+        <f t="shared" ref="A24:G24" si="1">A1</f>
+        <v>iteration/time step [SARSA]</v>
+      </c>
+      <c r="B24" s="2">
+        <f t="shared" si="1"/>
+        <v>1000</v>
+      </c>
+      <c r="C24" s="2">
+        <f t="shared" si="1"/>
+        <v>10000</v>
+      </c>
+      <c r="D24" s="2">
+        <f t="shared" si="1"/>
+        <v>100000</v>
+      </c>
+      <c r="E24" s="2">
+        <f t="shared" si="1"/>
+        <v>1000000</v>
+      </c>
+      <c r="F24" s="2">
+        <f t="shared" si="1"/>
+        <v>10000000</v>
+      </c>
+      <c r="G24" s="2">
+        <f t="shared" si="1"/>
+        <v>100000000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A25" s="2" t="str">
+        <f t="shared" ref="A25:G25" si="2">A12</f>
+        <v>Average [SARSA]</v>
+      </c>
+      <c r="B25" s="2">
+        <f t="shared" si="2"/>
+        <v>-6.3343276236604434E-2</v>
+      </c>
+      <c r="C25" s="2">
+        <f t="shared" si="2"/>
+        <v>-9.6029837040099209E-2</v>
+      </c>
+      <c r="D25" s="2">
+        <f t="shared" si="2"/>
+        <v>-5.0835668454106163E-2</v>
+      </c>
+      <c r="E25" s="2">
+        <f t="shared" si="2"/>
+        <v>-7.6170876878871849E-2</v>
+      </c>
+      <c r="F25" s="2">
+        <f t="shared" si="2"/>
+        <v>-6.9940151255909563E-2</v>
+      </c>
+      <c r="G25" s="2">
+        <f t="shared" si="2"/>
+        <v>-3.4748687940742908E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{134F64C0-2CFD-437B-9802-FEB9E0FE54D7}">
   <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -2995,61 +10765,61 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="str">
-        <f>A1</f>
+        <f t="shared" ref="A24:G24" si="0">A1</f>
         <v>iteration/time step</v>
       </c>
       <c r="B24" s="2">
-        <f>B1</f>
+        <f t="shared" si="0"/>
         <v>1000</v>
       </c>
       <c r="C24" s="2">
-        <f>C1</f>
+        <f t="shared" si="0"/>
         <v>10000</v>
       </c>
       <c r="D24" s="2">
-        <f>D1</f>
+        <f t="shared" si="0"/>
         <v>100000</v>
       </c>
       <c r="E24" s="2">
-        <f>E1</f>
+        <f t="shared" si="0"/>
         <v>1000000</v>
       </c>
       <c r="F24" s="2">
-        <f>F1</f>
+        <f t="shared" si="0"/>
         <v>10000000</v>
       </c>
       <c r="G24" s="2">
-        <f>G1</f>
+        <f t="shared" si="0"/>
         <v>100000000</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="str">
-        <f>A12</f>
+        <f t="shared" ref="A25:G25" si="1">A12</f>
         <v>Average</v>
       </c>
       <c r="B25" s="2">
-        <f>B12</f>
+        <f t="shared" si="1"/>
         <v>0.17533869343329442</v>
       </c>
       <c r="C25" s="2">
-        <f>C12</f>
+        <f t="shared" si="1"/>
         <v>0.12342384583238049</v>
       </c>
       <c r="D25" s="2">
-        <f>D12</f>
+        <f t="shared" si="1"/>
         <v>0.19173486989629204</v>
       </c>
       <c r="E25" s="2">
-        <f>E12</f>
+        <f t="shared" si="1"/>
         <v>0.19686953049049599</v>
       </c>
       <c r="F25" s="2">
-        <f>F12</f>
+        <f t="shared" si="1"/>
         <v>0.15502010843522235</v>
       </c>
       <c r="G25" s="2">
-        <f>G12</f>
+        <f t="shared" si="1"/>
         <v>0.15190640647955672</v>
       </c>
     </row>
